--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.93075299175302</v>
+        <v>8.113747361159867</v>
       </c>
       <c r="D2" t="n">
-        <v>50.69630263851147</v>
+        <v>8.238149178758114</v>
       </c>
       <c r="E2" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F2" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.08294731379264</v>
+        <v>6.188478938491304</v>
       </c>
       <c r="D3" t="n">
-        <v>38.85351015264732</v>
+        <v>6.313695399805191</v>
       </c>
       <c r="E3" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F3" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.60499315787794</v>
+        <v>3.998311388155165</v>
       </c>
       <c r="D4" t="n">
-        <v>24.89086024579054</v>
+        <v>4.044764789940963</v>
       </c>
       <c r="E4" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F4" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.50196124977958</v>
+        <v>2.844068703089181</v>
       </c>
       <c r="D5" t="n">
-        <v>17.67070348192166</v>
+        <v>2.87148931581227</v>
       </c>
       <c r="E5" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F5" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.24975757155212</v>
+        <v>5.56558560537722</v>
       </c>
       <c r="D6" t="n">
-        <v>34.22998383002495</v>
+        <v>5.562372372379055</v>
       </c>
       <c r="E6" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F6" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.580458455400484</v>
+        <v>1.556824499002579</v>
       </c>
       <c r="D7" t="n">
-        <v>9.559654035927517</v>
+        <v>1.553443780838222</v>
       </c>
       <c r="E7" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F7" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.67503769661864</v>
+        <v>6.447193625700529</v>
       </c>
       <c r="D8" t="n">
-        <v>38.98667231874408</v>
+        <v>6.335334251795913</v>
       </c>
       <c r="E8" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F8" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.52080918318689</v>
+        <v>4.797131492267869</v>
       </c>
       <c r="D9" t="n">
-        <v>29.49527353808915</v>
+        <v>4.792981949939486</v>
       </c>
       <c r="E9" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F9" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.33164340892646</v>
+        <v>4.928892053950549</v>
       </c>
       <c r="D10" t="n">
-        <v>30.27843814226081</v>
+        <v>4.920246198117382</v>
       </c>
       <c r="E10" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F10" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.4828590953105</v>
+        <v>6.415964602987957</v>
       </c>
       <c r="D11" t="n">
-        <v>39.42216599132928</v>
+        <v>6.406101973591008</v>
       </c>
       <c r="E11" t="n">
-        <v>11.18018514768105</v>
+        <v>1.816780086498171</v>
       </c>
       <c r="F11" t="n">
-        <v>11.27196541115064</v>
+        <v>1.83169437931198</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
